--- a/artfynd/A 31242-2025 artfynd.xlsx
+++ b/artfynd/A 31242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840040</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31242-2025 artfynd.xlsx
+++ b/artfynd/A 31242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840040</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31242-2025 artfynd.xlsx
+++ b/artfynd/A 31242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840040</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31242-2025 artfynd.xlsx
+++ b/artfynd/A 31242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840040</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31242-2025 artfynd.xlsx
+++ b/artfynd/A 31242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840040</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31242-2025 artfynd.xlsx
+++ b/artfynd/A 31242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840040</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31242-2025 artfynd.xlsx
+++ b/artfynd/A 31242-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127840040</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
